--- a/output/pdf_financials_xlsx/FOX.xlsx
+++ b/output/pdf_financials_xlsx/FOX.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/FOX.xlsx
+++ b/output/pdf_financials_xlsx/FOX.xlsx
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $(2,036,979) $(1,173,419)</t>
+          <t>Net loss and comprehensive loss                                               $(2,036,979)    $(1,173,419)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $(1,173,419) $(1,414,198)</t>
+          <t>Net loss and comprehensive loss                                               $(1,173,419)    $(1,414,198)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">

--- a/output/pdf_financials_xlsx/FOX.xlsx
+++ b/output/pdf_financials_xlsx/FOX.xlsx
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.141115</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.257778</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.434733</v>
       </c>
     </row>
     <row r="93">
@@ -3137,7 +3137,11 @@
           <t>Share based payment reserve (note 6 &amp; 14)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3166,7 +3170,11 @@
           <t>Warrant reserve (note 8)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.007900000000000001</v>
       </c>
@@ -3309,7 +3317,11 @@
           <t>Share based payment reserve (note 6)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>1.133215</v>
       </c>

--- a/output/pdf_financials_xlsx/FOX.xlsx
+++ b/output/pdf_financials_xlsx/FOX.xlsx
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.052742</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.050581</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.153733</v>
       </c>
     </row>
     <row r="13">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.414198</v>
+        <v>-1.46694</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.173419</v>
+        <v>-1.224</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.036979</v>
+        <v>-2.190712</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.414198</v>
+        <v>-1.46694</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.173419</v>
+        <v>-1.224</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.036979</v>
+        <v>-2.190712</v>
       </c>
     </row>
     <row r="30">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
